--- a/src/portas/portabilidad.xlsx
+++ b/src/portas/portabilidad.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,435 +506,7691 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1005091011</v>
+        <v>1128051223</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>44225</v>
+        <v>38371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manuela</t>
+          <t>GIOVANY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cortes Lozano</t>
+          <t>LOPEZ SOLANO</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3248001631</v>
+        <v>3006196447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473832</t>
+          <t xml:space="preserve"> 57101702502408750</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I2" t="n">
-        <v>13855</v>
+        <v>99680</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>46183524</t>
+          <t>56796230</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>180.81</t>
+          <t>162.66</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1017272688</v>
+        <v>1001818090</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42955</v>
+        <v>39700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brayan</t>
+          <t>BRAYAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Areiza</t>
+          <t>MUNIVE RANGEL</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3247180763</v>
+        <v>3244142203</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473833</t>
+          <t xml:space="preserve"> 57101702502408754</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I3" t="n">
-        <v>14145</v>
+        <v>28713</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>46183771</t>
+          <t>56796314</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>180.54</t>
+          <t>160.84</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1005091011</v>
+        <v>1130588130</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44225</v>
+        <v>38282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manuela</t>
+          <t>FANNY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cortes Lozano</t>
+          <t>TORRES TREJOS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3248001640</v>
+        <v>3244136345</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473834</t>
+          <t xml:space="preserve"> 57101702502408756</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I4" t="n">
-        <v>25847</v>
+        <v>50864</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>46184060</t>
+          <t>56796413</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>182.73</t>
+          <t>169.21</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1007142873</v>
+        <v>1022972942</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43475</v>
+        <v>40158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Flor Angela</t>
+          <t>YHONNY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Muñoz Arias</t>
+          <t>BARON RIVERA</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3247179524</v>
+        <v>3007116763</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473835</t>
+          <t xml:space="preserve"> 57101702502408758</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I5" t="n">
-        <v>21862</v>
+        <v>69379</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>46184331</t>
+          <t>56796507</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>182.53</t>
+          <t>167.73</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1007142873</v>
+        <v>1087194318</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>43475</v>
+        <v>40498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Flor Angela</t>
+          <t>DELIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Muñoz Arias</t>
+          <t>MONSALVE CABEZAS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3247180752</v>
+        <v>3244120440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473836</t>
+          <t xml:space="preserve"> 57101702502408898</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I6" t="n">
-        <v>34738</v>
+        <v>32527</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>46184588</t>
+          <t>56796605</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>182.58</t>
+          <t>178.42</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1007142873</v>
+        <v>1106738115</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>43475</v>
+        <v>38140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Flor Angela</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Muñoz Arias</t>
+          <t>ARIAS VERGARA</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3247182559</v>
+        <v>3244133259</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473837</t>
+          <t xml:space="preserve"> 57101702502408900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I7" t="n">
-        <v>59282</v>
+        <v>33347</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>46184850</t>
+          <t>56796694</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>182.17</t>
+          <t>165.15</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1007142873</v>
+        <v>1106771241</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>43475</v>
+        <v>38526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flor Angela</t>
+          <t>YURY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Muñoz Arias</t>
+          <t>ACUÑA MORALES</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3247182547</v>
+        <v>3244136607</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473838</t>
+          <t xml:space="preserve"> 57101702502408901</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I8" t="n">
-        <v>48750</v>
+        <v>53844</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>46185095</t>
+          <t>56796769</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>182.98</t>
+          <t>174.82</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1065911419</v>
+        <v>1110504013</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>42249</v>
+        <v>39772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jhon Javier</t>
+          <t>PAULA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Gutiérrez Álvarez</t>
+          <t>LOMBANA SIERRA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3248001624</v>
+        <v>3244122199</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 57101602707473839</t>
+          <t xml:space="preserve"> 57101702502408927</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>33107232</v>
+        <v>1128390723</v>
       </c>
       <c r="I9" t="n">
-        <v>56022</v>
+        <v>91570</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>swan2073@hotmail.com</t>
+          <t>master.33@gmail.com</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepago </t>
+          <t>prepago</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>46185470</t>
+          <t>56796888</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>180.54</t>
+          <t>162.68</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1121862409</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>39534</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RUTH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OLARTE VERA</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3007126561</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702502408934</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I10" t="n">
+        <v>53115</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1022366393</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>39836</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DIANA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HERRERA CARRION</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3004843216</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702502408938</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I11" t="n">
+        <v>70924</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1032427148</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RAUL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3001929700</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650528</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I12" t="n">
+        <v>89400</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>53129976</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KELLY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MATEUS</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3246719249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650529</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I13" t="n">
+        <v>15244</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10317246</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ARMANDO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SAMBONI</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3244118955</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650530</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33304</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1007277765</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>KATHERINE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3001930052</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650531</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I15" t="n">
+        <v>26402</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1056482412</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>39002</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>YESID</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3245436254</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650532</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15054</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1002423615</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CRISTIAN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BARRIOSNUEVO</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3007120485</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650533</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I17" t="n">
+        <v>38246</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1020755486</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MILTON</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3004853932</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650534</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I18" t="n">
+        <v>86202</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1143435500</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JONATHAN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3244125446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650535</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I19" t="n">
+        <v>86743</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1049629323</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>40288</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WIENER</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3246739895</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650536</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I20" t="n">
+        <v>48104</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1111770983</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LENISA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NOVITENO</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3001922032</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650537</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I21" t="n">
+        <v>51264</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1014193360</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>38917</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SANDRA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ROCHA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3244371058</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650538</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I22" t="n">
+        <v>70951</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1077427414</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>38393</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JHOMAIRA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3004706973</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650539</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I23" t="n">
+        <v>35479</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1039082517</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>38555</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RUTH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HEREDIA</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3004654617</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650540</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I24" t="n">
+        <v>89395</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>72342463</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>38001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LUIS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3004820333</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650541</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I25" t="n">
+        <v>95540</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1143225764</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>39181</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3001889640</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650542</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I26" t="n">
+        <v>33702</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1075626955</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>40128</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JOSE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PULIDO</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3001939597</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650543</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I27" t="n">
+        <v>47666</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1042443781</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>40533</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>YURANIS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MANJARRES</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3004693102</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650544</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I28" t="n">
+        <v>35408</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1070324269</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>38078</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3004846574</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650545</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I29" t="n">
+        <v>94464</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1094899991</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>38992</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BLANCA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>QUISHPI</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3001891326</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650547</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I30" t="n">
+        <v>61173</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1060102654</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>39297</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DIZU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3001923407</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650548</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I31" t="n">
+        <v>95487</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1110506320</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>39834</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LUIS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MANCILLA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3002088807</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650555</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I32" t="n">
+        <v>68206</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1129567310</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>38180</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JESSICA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3001941699</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650556</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I33" t="n">
+        <v>64683</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1088286960</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>39878</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ANGELY</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PERDOMO</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3004695036</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650557</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6705</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1088946194</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>40513</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JESUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NARVAEZ</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3001949006</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650562</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I35" t="n">
+        <v>34331</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1017167395</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>39147</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>JARAMILLO</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3004868677</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650563</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I36" t="n">
+        <v>34449</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1074129809</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>38743</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WILMER</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3004845215</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650564</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I37" t="n">
+        <v>36000</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1018414001</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>38672</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JHONATHAN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ESLAVA</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3004695772</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650565</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I38" t="n">
+        <v>14266</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1140820844</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>39211</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FABIO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3004658952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650566</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I39" t="n">
+        <v>22193</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1073683582</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>39342</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NURY</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3004842178</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650583</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I40" t="n">
+        <v>36158</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1122649548</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>40210</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EIDY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3245436793</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650584</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I41" t="n">
+        <v>191</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1096183243</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>38145</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FREIMAR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PEÑALOZA</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3011714408</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507650602</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I42" t="n">
+        <v>30899</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1116776669</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MORERAS</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3004658782</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958698</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I43" t="n">
+        <v>96236</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1130597663</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>38777</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GISELLE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PELAEZ</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3004659127</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958699</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I44" t="n">
+        <v>16897</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1032375265</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>38323</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ASTRID</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OROZCO</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3013912939</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958700</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10115</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1123860519</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>38368</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JHON</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3004648962</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958723</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I46" t="n">
+        <v>76347</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1020725387</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>38541</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JULIAN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BADILLO</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3245450482</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958724</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I47" t="n">
+        <v>80148</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1028008489</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>40385</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ESPINOSA</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3004846471</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958734</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1085915976</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>39401</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>YILMAR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3001891174</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958735</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I49" t="n">
+        <v>11316</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1110480153</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>39111</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3246724012</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958736</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I50" t="n">
+        <v>37443</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1091805341</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>39638</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JESUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3001921398</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958737</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I51" t="n">
+        <v>83628</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1055313075</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>39546</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GIL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3245436261</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958738</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I52" t="n">
+        <v>98213</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1144045297</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>40008</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CAROLINA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CORREA</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3024529373</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958739</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I53" t="n">
+        <v>22798</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1019061793</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>40016</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JHONATHAN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3001931949</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958740</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I54" t="n">
+        <v>62001</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1042706223</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MARTA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>METAUTE</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3004841521</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958742</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I55" t="n">
+        <v>28315</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1082931425</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>39926</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ANTONNY</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CANTILLO</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3246108104</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958743</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I56" t="n">
+        <v>28878</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1110497725</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>JHON</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3001937612</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958745</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I57" t="n">
+        <v>25729</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1055832630</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>WEIMAR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GALVIS</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3011713985</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958748</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I58" t="n">
+        <v>33533</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1061113369</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>38392</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3001896396</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958749</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I59" t="n">
+        <v>41960</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1037498116</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MABEL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PUERTA</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3001929936</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958750</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3572</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1072647321</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ADRIANA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3246715514</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958751</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I61" t="n">
+        <v>88000</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1117509849</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>39413</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NINI</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3001890152</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958752</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I62" t="n">
+        <v>47974</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>80526076</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ARMANDO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MANCERA</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3004842213</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958753</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I63" t="n">
+        <v>81419</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1026277973</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ZULUAGA</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3001931902</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958757</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5502</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1112762074</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DIANA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MAYORGA</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>3004801691</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958758</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I65" t="n">
+        <v>24383</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1098662864</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ARED</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ORDUZ</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>3246744105</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958790</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I66" t="n">
+        <v>81467</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1014176390</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ANYI</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3013851589</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958801</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I67" t="n">
+        <v>72928</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>60267612</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>37673</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LAURA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3004694748</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958802</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I68" t="n">
+        <v>87842</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1051669130</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SINDY</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GALVIS</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3004845207</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958803</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I69" t="n">
+        <v>86175</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1116236361</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MILEIDY</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ARANGO</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3001922019</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958804</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I70" t="n">
+        <v>8713</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1091665857</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>KEILY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BAYONA</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3245436845</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958805</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I71" t="n">
+        <v>81913</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1118839639</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>JHON</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3001891218</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958806</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I72" t="n">
+        <v>60526</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1144031131</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3244477353</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958807</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I73" t="n">
+        <v>69582</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1024534968</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>JEISON</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PEÑA</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3004870646</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958899</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I74" t="n">
+        <v>87265</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1065627597</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>YONATHAN</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>JACOME</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3004812200</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958957</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I75" t="n">
+        <v>51823</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1041261601</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>YEFERSON</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ROSALES</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>3001914124</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958972</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I76" t="n">
+        <v>73652</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1144146483</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>39863</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>JOHANA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>3004650815</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958973</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I77" t="n">
+        <v>10080</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1033690067</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VERONICA</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BEDOYA</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>3004852104</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958974</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I78" t="n">
+        <v>44595</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>80076304</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OMAR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RUANO</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3001941840</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958975</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I79" t="n">
+        <v>39914</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>32358650</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SIRLEY</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DOMICO</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>3009084801</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958976</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I80" t="n">
+        <v>56465</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1068663590</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HUALENA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MONTES</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>3004852060</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958977</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I81" t="n">
+        <v>42658</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1074185118</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DORIS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>3001891162</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958978</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I82" t="n">
+        <v>90683</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>75105299</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NORWIN</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ZAPATA</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3244890373</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958979</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5719</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1069738166</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>YENY</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GUASCA</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>3015815482</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958980</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I84" t="n">
+        <v>31281</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1121835689</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MARCO</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3004641232</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958981</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7115</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1082156090</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ANGELA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PRADA</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3001924167</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958982</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I86" t="n">
+        <v>77547</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1128428838</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>JOHNNY</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>3001913933</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958983</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I87" t="n">
+        <v>64050</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>41962216</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CLAUDIA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>QUIMBAYO</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>3001921564</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958984</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I88" t="n">
+        <v>21224</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1035223012</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CRISTINA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>3004647037</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958985</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I89" t="n">
+        <v>77295</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>53102659</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ANDREA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PUENTES</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3004868719</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958986</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I90" t="n">
+        <v>85408</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1062676457</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KATRIN</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3244150762</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958987</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I91" t="n">
+        <v>71944</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1144138625</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FALLON</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LOBATON</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>3001924993</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958988</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I92" t="n">
+        <v>67559</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>38796273</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>3001889714</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958989</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I93" t="n">
+        <v>82781</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>87533385</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BASTIDAS</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>3013884870</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958990</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3511</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1136884148</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>40340</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ANDRES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3013916448</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958991</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I95" t="n">
+        <v>86578</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1068815414</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OMAR</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VERTEL</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>3001891189</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958992</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I96" t="n">
+        <v>43173</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1151442556</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MARLON</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VENTE</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3004807380</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958993</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I97" t="n">
+        <v>75627</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1073163268</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>YONATHAN</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BONILLA</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>3001890177</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958994</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I98" t="n">
+        <v>16711</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1018345495</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>3004650774</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958995</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I99" t="n">
+        <v>81644</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1046872190</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>40060</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>KAREN</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3001924779</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958996</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I100" t="n">
+        <v>30838</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1101875348</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>39821</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>YAJAIRA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>MORELO</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3001924868</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958997</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I101" t="n">
+        <v>81495</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1110445383</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>38112</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>JULIAN</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SANDOVAL</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>3004870985</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958998</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I102" t="n">
+        <v>75090</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1140839851</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>FARELO</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>3001949182</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507958999</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I103" t="n">
+        <v>48021</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1088292022</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>YEACK</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>3244150740</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959000</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I104" t="n">
+        <v>67946</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>53075741</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>37788</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DIANA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GUAUQUE</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>3001939642</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959001</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I105" t="n">
+        <v>45104</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1116547919</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NOHORA</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>3011714477</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959002</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I106" t="n">
+        <v>26915</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1053813677</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>40101</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ADRIANA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GIRALDO</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>3244152938</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959003</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I107" t="n">
+        <v>43499</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>16379998</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>37911</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CARLOS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CALDON</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>3001949186</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959004</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I108" t="n">
+        <v>59854</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1105871211</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>YULIET</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>3004656407</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959005</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I109" t="n">
+        <v>26501</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1065598894</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>JANER</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>REALES</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>3001929732</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959006</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I110" t="n">
+        <v>51159</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1114885810</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>JULIAN</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OCORO</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>3014209745</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959007</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I111" t="n">
+        <v>19371</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1083876744</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>38938</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>3244118945</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959008</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I112" t="n">
+        <v>30531</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>74348353</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>HUGO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>3246704998</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959009</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I113" t="n">
+        <v>83924</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1130623221</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>JOAN</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>MURILLO</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3001889644</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959010</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I114" t="n">
+        <v>7306</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1070954510</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>39281</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>3001895243</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959011</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I115" t="n">
+        <v>28640</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1094779206</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ALFONSO</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VILLAMIZAR</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>3001889742</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959012</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I116" t="n">
+        <v>48204</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1102837034</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>39840</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ANDRES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>MENESES</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>3016026031</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959013</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I117" t="n">
+        <v>21876</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1047382009</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>38355</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>LUIS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GORDILLO</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3016048238</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959014</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I118" t="n">
+        <v>80021</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1129532206</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>38357</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MAYLEEN</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CAVADIA</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>3004810641</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959015</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I119" t="n">
+        <v>50428</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1115070052</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>39128</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>JOAN</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ROSERO</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>3004811014</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959016</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I120" t="n">
+        <v>54679</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1098634709</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>38490</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ANDREA</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>3244118874</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959017</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5675</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1092335894</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>38217</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RICARDO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>TRIANA</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>3001924209</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959018</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I122" t="n">
+        <v>80974</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>67030990</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>38006</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>JENNY</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ARANA</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>3244373095</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959019</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I123" t="n">
+        <v>70400</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1111762581</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>39014</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>JEYSON</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>RIVAS</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>3108474668</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959020</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I124" t="n">
+        <v>30098</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1045667921</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>38730</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>GRASSE</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>MIRANDA</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>3015989127</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959021</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I125" t="n">
+        <v>20527</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1117493848</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>38520</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>LILIAN</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CARDOZO</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>3004802884</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959022</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I126" t="n">
+        <v>28632</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1193141518</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>40009</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>YAISETH</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>3001921436</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959023</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I127" t="n">
+        <v>15669</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1064488948</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>39722</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>OCORO</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3004868474</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959024</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I128" t="n">
+        <v>78658</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1082893724</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>39183</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BRIGITTE</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>3004868592</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959025</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I129" t="n">
+        <v>13695</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>29974673</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>37812</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ANDREA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CANTILLO</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>3244121300</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959026</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4305</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>32150811</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>37683</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MARCELA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LOPERA</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3013245381</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959027</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I131" t="n">
+        <v>75593</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1004825984</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>39420</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DIEGO</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>FLOREZ</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>3006231920</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959028</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3303</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1144132372</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>39427</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>HERNAN</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ARANGO</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>3244150710</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959029</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I133" t="n">
+        <v>58590</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1128327374</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>39932</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>LISETH</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>3001939724</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959030</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I134" t="n">
+        <v>4851</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1060100552</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>38204</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JAVIER</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BOMBA</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3001416683</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959031</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I135" t="n">
+        <v>81512</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1007507419</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>40038</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>EVELIO</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CORREA</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>3244121365</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959032</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2086</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1023908616</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>39988</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MARYORY</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AGAMEZ</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>3004868660</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959033</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I137" t="n">
+        <v>68260</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1079032039</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>38014</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>HENRY</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>3004840413</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959034</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I138" t="n">
+        <v>64744</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1096906388</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>39157</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AYALA</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3006231225</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959035</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I139" t="n">
+        <v>97105</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1083460162</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>38896</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>LEONARDO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>3013910388</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959036</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I140" t="n">
+        <v>14290</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1075235040</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>39148</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OSUNA</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>3004861014</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959037</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2226</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1017181755</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>39637</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NYNY</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SEPULVEDA</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>3013897108</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959038</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I142" t="n">
+        <v>12446</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1036933804</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>39204</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ARBELAEZ</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>3007772912</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959039</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I143" t="n">
+        <v>14102</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1128265791</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>38258</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>3244121247</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959040</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I144" t="n">
+        <v>45884</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1043872063</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>39104</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DEIVIS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CANTILLO</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3001889616</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959041</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I145" t="n">
+        <v>53124</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>94544129</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>37853</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ROBINSON</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>3004134227</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959042</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I146" t="n">
+        <v>86543</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1085284150</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>39736</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>JIYARDIN</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>3244121168</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959043</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I147" t="n">
+        <v>13391</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1051416981</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DAMIAN</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>3004653020</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959044</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I148" t="n">
+        <v>63545</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1133924039</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>38257</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AYDA</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>3004695605</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959045</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I149" t="n">
+        <v>70853</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1053794753</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>39205</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>3004656461</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959046</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I150" t="n">
+        <v>69097</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1098733884</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>40591</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>YULIAN</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>GIRALDO</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>3244373107</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959047</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I151" t="n">
+        <v>82763</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1061219521</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>38674</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>YIYI</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>YUGUE</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>3004693348</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959048</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I152" t="n">
+        <v>19851</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1078116654</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SANDRA</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>3244121281</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959049</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I153" t="n">
+        <v>88911</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1037546011</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>YEISON</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ESPINOSA</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>3013851426</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959050</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I154" t="n">
+        <v>93852</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1054918074</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>38742</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ERICA</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>MARIN</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>3015815570</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507959051</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2338</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1120865048</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>38477</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DEYANIRA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AMAYA</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>3001931936</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961696</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I156" t="n">
+        <v>35011</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1085286214</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>39855</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DEIVY</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NARVAEZ</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>3004818783</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961697</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I157" t="n">
+        <v>23205</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>94558061</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>38005</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>YIBER</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>MONDRAGON</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>3006256078</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961698</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I158" t="n">
+        <v>97713</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1086194909</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>39497</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ESTUPIÑAN</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>3001896099</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961699</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I159" t="n">
+        <v>9127</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1023723324</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>40149</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>YEISON</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>3001933114</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961700</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I160" t="n">
+        <v>92266</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>1046399111</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>38951</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>RANEL</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>3244373132</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961702</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I161" t="n">
+        <v>24056</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1109417358</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>40368</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>JULIAN</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CANAS</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>3245436164</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961703</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I162" t="n">
+        <v>31552</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1084923606</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DIANA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>3244150670</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961704</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I163" t="n">
+        <v>10453</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1073155546</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>39009</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>JOSE</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TABARES</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>3015989251</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101702507961705</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="n">
+        <v>1128390723</v>
+      </c>
+      <c r="I164" t="n">
+        <v>56105</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>master.33@gmail.com</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>prepago</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
